--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - VENTAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2192" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E39E9F8-A42B-4FB1-8B8B-93549D42DFD7}"/>
+  <xr:revisionPtr revIDLastSave="2201" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97CE527-433C-4A31-9CCC-C952E00E7A29}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja2" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$6326</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja2!$A$1:$H$6330</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12126" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12142" uniqueCount="94">
   <si>
     <t>Sucursal</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>Bibiana Farley Rios Agudelo</t>
+  </si>
+  <si>
+    <t>Coordinador y Supervisora</t>
   </si>
 </sst>
 </file>
@@ -694,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A324D6B-D2A7-463C-9FF3-0E9F0C270E00}">
-  <dimension ref="A1:H6326"/>
+  <dimension ref="A1:H6330"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -79179,133 +79182,177 @@
         <v>46148</v>
       </c>
       <c r="B3019" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3019" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="C3019">
+        <v>98667259</v>
+      </c>
+      <c r="D3019" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3019" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3019" s="3" t="s">
+        <v>70</v>
       </c>
       <c r="G3019">
-        <v>0</v>
-      </c>
-      <c r="H3019"/>
+        <v>29</v>
+      </c>
+      <c r="H3019" s="1">
+        <v>622.35000000000014</v>
+      </c>
     </row>
     <row r="3020" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3020" s="2">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B3020" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3020" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="C3020">
+        <v>98667259</v>
+      </c>
+      <c r="D3020" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3020" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3020" s="3" t="s">
+        <v>72</v>
       </c>
       <c r="G3020">
-        <v>438</v>
-      </c>
-      <c r="H3020"/>
+        <v>1628</v>
+      </c>
+      <c r="H3020" s="1">
+        <v>2800</v>
+      </c>
     </row>
     <row r="3021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3021" s="2">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B3021" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3021" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="C3021">
+        <v>98667259</v>
+      </c>
+      <c r="D3021" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3021" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3021" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="G3021">
-        <v>0</v>
-      </c>
-      <c r="H3021"/>
+        <v>440</v>
+      </c>
+      <c r="H3021" s="1">
+        <v>4774.2500000000055</v>
+      </c>
     </row>
     <row r="3022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3022" s="2">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="B3022" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3022" t="s">
-        <v>82</v>
+        <v>77</v>
+      </c>
+      <c r="C3022">
+        <v>98667259</v>
+      </c>
+      <c r="D3022" t="s">
+        <v>93</v>
+      </c>
+      <c r="E3022" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3022" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="G3022">
-        <v>179</v>
-      </c>
-      <c r="H3022"/>
+        <v>872</v>
+      </c>
+      <c r="H3022" s="1">
+        <v>15796.579999999931</v>
+      </c>
     </row>
     <row r="3023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3023" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B3023" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F3023" t="s">
         <v>82</v>
       </c>
       <c r="G3023">
-        <v>364</v>
+        <v>0</v>
       </c>
       <c r="H3023"/>
     </row>
     <row r="3024" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3024" s="2">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B3024" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F3024" t="s">
         <v>82</v>
       </c>
       <c r="G3024">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="H3024"/>
     </row>
     <row r="3025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3025" s="2">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="B3025" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F3025" t="s">
         <v>82</v>
       </c>
       <c r="G3025">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="H3025"/>
     </row>
     <row r="3026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3026" s="2">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="B3026" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="F3026" t="s">
         <v>82</v>
       </c>
       <c r="G3026">
-        <v>264</v>
+        <v>179</v>
       </c>
       <c r="H3026"/>
     </row>
     <row r="3027" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3027" s="2">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="B3027" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3027" t="s">
         <v>82</v>
       </c>
       <c r="G3027">
-        <v>259</v>
+        <v>364</v>
       </c>
       <c r="H3027"/>
     </row>
@@ -79314,13 +79361,13 @@
         <v>46149</v>
       </c>
       <c r="B3028" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F3028" t="s">
         <v>82</v>
       </c>
       <c r="G3028">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="H3028"/>
     </row>
@@ -79329,58 +79376,58 @@
         <v>46149</v>
       </c>
       <c r="B3029" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F3029" t="s">
         <v>82</v>
       </c>
       <c r="G3029">
-        <v>142</v>
+        <v>326</v>
       </c>
       <c r="H3029"/>
     </row>
     <row r="3030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3030" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B3030" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F3030" t="s">
         <v>82</v>
       </c>
       <c r="G3030">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="H3030"/>
     </row>
     <row r="3031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3031" s="2">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="B3031" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F3031" t="s">
         <v>82</v>
       </c>
       <c r="G3031">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="H3031"/>
     </row>
     <row r="3032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3032" s="2">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B3032" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="F3032" t="s">
         <v>82</v>
       </c>
       <c r="G3032">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="H3032"/>
     </row>
@@ -79389,133 +79436,133 @@
         <v>46149</v>
       </c>
       <c r="B3033" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F3033" t="s">
         <v>82</v>
       </c>
       <c r="G3033">
-        <v>369</v>
+        <v>142</v>
       </c>
       <c r="H3033"/>
     </row>
     <row r="3034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3034" s="2">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="B3034" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="F3034" t="s">
         <v>82</v>
       </c>
       <c r="G3034">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="H3034"/>
     </row>
     <row r="3035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3035" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B3035" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="F3035" t="s">
         <v>82</v>
       </c>
       <c r="G3035">
-        <v>399</v>
+        <v>235</v>
       </c>
       <c r="H3035"/>
     </row>
     <row r="3036" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3036" s="2">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B3036" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="F3036" t="s">
         <v>82</v>
       </c>
       <c r="G3036">
-        <v>111</v>
+        <v>354</v>
       </c>
       <c r="H3036"/>
     </row>
     <row r="3037" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3037" s="2">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="B3037" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F3037" t="s">
         <v>82</v>
       </c>
       <c r="G3037">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="H3037"/>
     </row>
     <row r="3038" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3038" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B3038" t="s">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="F3038" t="s">
         <v>82</v>
       </c>
       <c r="G3038">
-        <v>246</v>
+        <v>320</v>
       </c>
       <c r="H3038"/>
     </row>
     <row r="3039" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3039" s="2">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B3039" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="F3039" t="s">
         <v>82</v>
       </c>
       <c r="G3039">
-        <v>65</v>
+        <v>399</v>
       </c>
       <c r="H3039"/>
     </row>
     <row r="3040" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3040" s="2">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B3040" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F3040" t="s">
         <v>82</v>
       </c>
       <c r="G3040">
-        <v>417</v>
+        <v>111</v>
       </c>
       <c r="H3040"/>
     </row>
     <row r="3041" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3041" s="2">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="B3041" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="F3041" t="s">
         <v>82</v>
       </c>
       <c r="G3041">
-        <v>5944</v>
+        <v>388</v>
       </c>
       <c r="H3041"/>
     </row>
@@ -79524,45 +79571,89 @@
         <v>46146</v>
       </c>
       <c r="B3042" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="F3042" t="s">
         <v>82</v>
       </c>
       <c r="G3042">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="H3042"/>
     </row>
     <row r="3043" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3043" s="2">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B3043" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="F3043" t="s">
         <v>82</v>
       </c>
       <c r="G3043">
+        <v>65</v>
+      </c>
+      <c r="H3043"/>
+    </row>
+    <row r="3044" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3044" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B3044" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3044" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3044">
+        <v>417</v>
+      </c>
+      <c r="H3044"/>
+    </row>
+    <row r="3045" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3045" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B3045" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3045" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3045">
+        <v>5944</v>
+      </c>
+      <c r="H3045"/>
+    </row>
+    <row r="3046" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3046" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B3046" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3046" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3046">
         <v>0</v>
       </c>
-      <c r="H3043"/>
-    </row>
-    <row r="3044" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3044" s="2"/>
-      <c r="H3044"/>
-    </row>
-    <row r="3045" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3045" s="2"/>
-      <c r="H3045"/>
-    </row>
-    <row r="3046" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3046" s="2"/>
       <c r="H3046"/>
     </row>
     <row r="3047" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3047" s="2"/>
+      <c r="A3047" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B3047" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3047" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3047">
+        <v>0</v>
+      </c>
       <c r="H3047"/>
     </row>
     <row r="3048" spans="1:8" x14ac:dyDescent="0.25">
@@ -91583,35 +91674,35 @@
     </row>
     <row r="6052" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6052" s="2"/>
-      <c r="F6052" s="3"/>
+      <c r="H6052"/>
     </row>
     <row r="6053" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6053" s="2"/>
-      <c r="F6053" s="3"/>
+      <c r="H6053"/>
     </row>
     <row r="6054" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6054" s="2"/>
-      <c r="F6054" s="3"/>
+      <c r="H6054"/>
     </row>
     <row r="6055" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6055" s="2"/>
-      <c r="F6055" s="3"/>
+      <c r="H6055"/>
     </row>
     <row r="6056" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6056" s="2"/>
-      <c r="H6056"/>
+      <c r="F6056" s="3"/>
     </row>
     <row r="6057" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6057" s="2"/>
-      <c r="H6057"/>
+      <c r="F6057" s="3"/>
     </row>
     <row r="6058" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6058" s="2"/>
-      <c r="H6058"/>
+      <c r="F6058" s="3"/>
     </row>
     <row r="6059" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6059" s="2"/>
-      <c r="H6059"/>
+      <c r="F6059" s="3"/>
     </row>
     <row r="6060" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6060" s="2"/>
@@ -92571,72 +92662,76 @@
     </row>
     <row r="6299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6299" s="2"/>
-      <c r="F6299" s="3"/>
+      <c r="H6299"/>
     </row>
     <row r="6300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6300" s="2"/>
-      <c r="F6300" s="3"/>
+      <c r="H6300"/>
     </row>
     <row r="6301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6301" s="2"/>
-      <c r="F6301" s="3"/>
+      <c r="H6301"/>
     </row>
     <row r="6302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6302" s="2"/>
-      <c r="F6302" s="3"/>
+      <c r="H6302"/>
     </row>
     <row r="6303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6303" s="2"/>
+      <c r="F6303" s="3"/>
     </row>
     <row r="6304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6304" s="2"/>
-    </row>
-    <row r="6305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F6304" s="3"/>
+    </row>
+    <row r="6305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6305" s="2"/>
-    </row>
-    <row r="6306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F6305" s="3"/>
+    </row>
+    <row r="6306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6306" s="2"/>
-    </row>
-    <row r="6307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F6306" s="3"/>
+    </row>
+    <row r="6307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6307" s="2"/>
     </row>
-    <row r="6308" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6308" s="2"/>
     </row>
-    <row r="6309" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6309" s="2"/>
     </row>
-    <row r="6310" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6310" s="2"/>
     </row>
-    <row r="6311" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6311" s="2"/>
     </row>
-    <row r="6312" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6312" s="2"/>
     </row>
-    <row r="6313" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6313" s="2"/>
     </row>
-    <row r="6314" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6314" s="2"/>
     </row>
-    <row r="6315" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6315" s="2"/>
     </row>
-    <row r="6316" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6316" s="2"/>
     </row>
-    <row r="6317" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6317" s="2"/>
     </row>
-    <row r="6318" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6318" s="2"/>
     </row>
-    <row r="6319" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6319" s="2"/>
     </row>
-    <row r="6320" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6320" s="2"/>
     </row>
     <row r="6321" spans="1:1" x14ac:dyDescent="0.25">
@@ -92657,8 +92752,20 @@
     <row r="6326" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6326" s="2"/>
     </row>
+    <row r="6327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6327" s="2"/>
+    </row>
+    <row r="6328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6328" s="2"/>
+    </row>
+    <row r="6329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6329" s="2"/>
+    </row>
+    <row r="6330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6330" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H6326" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}"/>
+  <autoFilter ref="A1:H6330" xr:uid="{D750F336-D965-4F10-8ECD-FE069CE0072F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/data/liquidacion_final.xlsx
+++ b/data/liquidacion_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/05 Mayo/Liquidacióncvs - VENTAS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2201" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F97CE527-433C-4A31-9CCC-C952E00E7A29}"/>
+  <xr:revisionPtr revIDLastSave="2215" documentId="8_{B4C009C8-9220-4C9C-A445-506C3CDC0C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EEA8C16-0717-485E-91CA-B94277D11BA1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F96EC60D-8A4F-416C-B913-DA3C0AB122B4}"/>
   </bookViews>
@@ -28656,7 +28656,7 @@
         <v>1</v>
       </c>
       <c r="H1075">
-        <v>72.08</v>
+        <v>19.600000000000001</v>
       </c>
     </row>
     <row r="1076" spans="1:8" x14ac:dyDescent="0.25">
@@ -79278,7 +79278,7 @@
         <v>872</v>
       </c>
       <c r="H3022" s="1">
-        <v>15796.579999999931</v>
+        <v>15744</v>
       </c>
     </row>
     <row r="3023" spans="1:8" x14ac:dyDescent="0.25">
